--- a/config/xlsx/recipes.xlsx
+++ b/config/xlsx/recipes.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>7009;8009;3009;6009</t>
+          <t>7009;8009;3009;5009</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -802,7 +802,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>7010;8010;3010;6010</t>
+          <t>7010;8010;3010;5010</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -823,7 +823,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>7011;8011;3011;6011</t>
+          <t>7011;8011;3011;5011</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>7012;8012;9012;6012</t>
+          <t>7012;8012;10012;6012</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -865,7 +865,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>5009;5012;9009</t>
+          <t>6009;5012;9009</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>5010;5011;9010</t>
+          <t>6010;5011;9010</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>5011;9011;1010</t>
+          <t>6011;9011;1010</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>27004;27004</t>
+          <t>6004;9004</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>27002;9004</t>
+          <t>5002;9004</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>27003;6004;5004</t>
+          <t>5003;6004;5004</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>27005;6005;3005</t>
+          <t>5005;6005;3005</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>27008;6006;3006</t>
+          <t>1006;6006;3006</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>27009;6007;3007</t>
+          <t>1007;6007;3007</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>27010;6008;3008</t>
+          <t>1008;6008;3008</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>27011;6009;3009</t>
+          <t>1009;6009;3009</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>27012;6010;3010</t>
+          <t>1010;6010;3010</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>27013;6011;3011</t>
+          <t>1011;6011;3011</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>27014;6012;9012</t>
+          <t>1012;6012;9012</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>27023;6013;3013</t>
+          <t>8013;6013;3013</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>27024;6014;3014</t>
+          <t>8014;6014;3014</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>27025;6015;3015</t>
+          <t>8015;6015;3015</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>27026;6016;3016</t>
+          <t>8016;6016;3016</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>27013;27014;27023;3016</t>
+          <t>1011;1012;8013;3016</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>27024;27025;27026;4016</t>
+          <t>8014;8015;8016;4016</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>27006;27034;27019;27030</t>
+          <t>6004;3005;5012;3016</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>27013;27035;27038;27039</t>
+          <t>1011;3006;3009;3010</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>27045;27047;27046;9016</t>
+          <t>3016;4016;8016;9016</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>5012;9012</t>
+          <t>5012;10012</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>7013;8013;9013</t>
+          <t>7013;8013;10013</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>7014;8014;9014</t>
+          <t>7014;8014;10014</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>7015;8015;9015</t>
+          <t>7015;8015;10015</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>7016;8016;9016</t>
+          <t>7016;8016;10016</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>5013;6013;3013</t>
+          <t>5013;6013;1013</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>5014;6014;3014</t>
+          <t>1014;6014;3014</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>5015;6015;3015</t>
+          <t>1015;6015;3015</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>5016;6016;3016</t>
+          <t>1016;6016;3016</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>27002;3002</t>
+          <t>5002;3002</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>27004;9004;3004</t>
+          <t>5004;9004;3004</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>27005;3005;6005</t>
+          <t>10005;3005;6005</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>27008;3006;6006</t>
+          <t>10006;3006;6006</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>27009;3007;6007</t>
+          <t>10007;3007;6007</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>27010;3008;6008</t>
+          <t>10008;3008;6008</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>27011;3009;6009</t>
+          <t>7009;3009;6009</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>27012;3010;6010</t>
+          <t>7010;3010;6010</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>27013;3011;6011</t>
+          <t>7011;3011;6011</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>27014;9012;6012</t>
+          <t>7012;9012;6012</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>27023;3013;6013</t>
+          <t>7013;3013;6013</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>27024;3014;6014</t>
+          <t>7014;3014;6014</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>27025;3015;6015</t>
+          <t>7015;3015;6015</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>27026;3016;6016</t>
+          <t>7016;3016;6016</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>27082;27087;27090</t>
+          <t>3004;3009;6012</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>27092;27093;27094</t>
+          <t>3014;3015;3016</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>27085;27084;27087;27088</t>
+          <t>3007;3006;3009;3010</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>27051;27054;27068;27080</t>
+          <t>1001;3004;6012;3016</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>6004;9004;3004</t>
+          <t>6004;10004;3004</t>
         </is>
       </c>
       <c r="D130" s="3" t="n">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>6012;9012;5012</t>
+          <t>6012;9012;10012</t>
         </is>
       </c>
       <c r="D134" s="3" t="n">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>27051;27054;27068</t>
+          <t>3001;3004;6012</t>
         </is>
       </c>
       <c r="D143" s="3" t="n">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>27108;27107;27110;27111</t>
+          <t>3007;3006;3009;3010</t>
         </is>
       </c>
       <c r="D145" s="3" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>27118;27119;27120;27121</t>
+          <t>3005;3006;3007;3008</t>
         </is>
       </c>
       <c r="D147" s="3" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>27115;27127;27136;5014</t>
+          <t>1014;8014;6014;5014</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>27116;27128;27137;5015</t>
+          <t>1015;8015;6015;5015</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>27117;27129;27138;5016</t>
+          <t>1016;8016;6016;5016</t>
         </is>
       </c>
       <c r="D150" s="3" t="n">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>2010;4010;27060;3010</t>
+          <t>2010;4010;6010;3010</t>
         </is>
       </c>
       <c r="D160" s="3" t="n">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>7003;8003;9002;3002</t>
+          <t>7003;8003;10002;3002</t>
         </is>
       </c>
       <c r="D185" s="3" t="n">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>1002;5002;9002</t>
+          <t>1002;5002;10002</t>
         </is>
       </c>
       <c r="D199" s="3" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>1003;5004;9004;3004</t>
+          <t>1003;5004;10004;3004</t>
         </is>
       </c>
       <c r="D200" s="3" t="n">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>1004;1005;27004;4004</t>
+          <t>1004;1005;5004;4004</t>
         </is>
       </c>
       <c r="D201" s="3" t="n">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>1009;1010;27007;4009</t>
+          <t>1009;1010;6005;4009</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>1012;2009;27009;8012</t>
+          <t>1012;2009;6007;8012</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
